--- a/training_results.xlsx
+++ b/training_results.xlsx
@@ -2149,27 +2149,6 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="str">
-        <v>2026-05-22 00:56:16</v>
-      </c>
-      <c r="B34" t="str">
-        <v>CIFAR10</v>
-      </c>
-      <c r="C34" t="str">
-        <v>32</v>
-      </c>
-      <c r="D34" t="str">
-        <v>40</v>
-      </c>
-      <c r="E34" t="str">
-        <v>40</v>
-      </c>
-      <c r="F34" t="str">
-        <v>0.01</v>
-      </c>
-      <c r="G34" t="str">
-        <v>5</v>
-      </c>
       <c r="H34" t="str">
         <v/>
       </c>
@@ -2178,24 +2157,6 @@
       </c>
       <c r="J34" t="str">
         <v/>
-      </c>
-      <c r="K34" t="str">
-        <v>98.48</v>
-      </c>
-      <c r="L34" t="str">
-        <v>92.21</v>
-      </c>
-      <c r="M34" t="str">
-        <v>93.31</v>
-      </c>
-      <c r="N34" t="str">
-        <v>0.2535</v>
-      </c>
-      <c r="O34" t="str">
-        <v>models/densenet_model_cifar10_32batch_40epochs_0.01lr.pth</v>
-      </c>
-      <c r="P34" t="str">
-        <v>cuda</v>
       </c>
       <c r="Q34" t="str">
         <v/>
